--- a/resources/templates/standard/A4100-04.xlsx
+++ b/resources/templates/standard/A4100-04.xlsx
@@ -11,7 +11,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>자료 관리 대장</t>
   </si>
@@ -558,12 +561,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.95" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -598,7 +603,7 @@
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM1" s="3"/>
       <c r="AN1" s="3"/>
@@ -649,7 +654,7 @@
       <c r="AJ2" s="2"/>
       <c r="AK2" s="2"/>
       <c r="AL2" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM2" s="4"/>
       <c r="AN2" s="4"/>
@@ -663,18 +668,18 @@
     </row>
     <row r="3" ht="18.6" customHeight="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
@@ -682,11 +687,11 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" s="3"/>
       <c r="P3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
@@ -715,7 +720,7 @@
       <c r="AO3" s="3"/>
       <c r="AP3" s="3"/>
       <c r="AQ3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR3" s="3"/>
       <c r="AS3" s="3"/>
@@ -739,39 +744,39 @@
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="6"/>
       <c r="R4" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="S4" s="6"/>
       <c r="T4" s="6"/>
       <c r="U4" s="6"/>
       <c r="V4" s="6"/>
       <c r="W4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="X4" s="6"/>
       <c r="Y4" s="6"/>
       <c r="Z4" s="6"/>
       <c r="AA4" s="6"/>
       <c r="AB4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC4" s="6"/>
       <c r="AD4" s="6"/>
       <c r="AE4" s="6"/>
       <c r="AF4" s="6"/>
       <c r="AG4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH4" s="6"/>
       <c r="AI4" s="6"/>
       <c r="AJ4" s="6"/>
       <c r="AK4" s="6"/>
       <c r="AL4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AM4" s="6"/>
       <c r="AN4" s="6"/>
@@ -800,7 +805,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
       <c r="P5" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q5" s="8"/>
       <c r="R5" s="8"/>
@@ -851,7 +856,7 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
       <c r="P6" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q6" s="9"/>
       <c r="R6" s="9"/>
@@ -902,7 +907,7 @@
       <c r="N7" s="6"/>
       <c r="O7" s="6"/>
       <c r="P7" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
@@ -953,7 +958,7 @@
       <c r="N8" s="6"/>
       <c r="O8" s="6"/>
       <c r="P8" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q8" s="9"/>
       <c r="R8" s="9"/>
@@ -1004,7 +1009,7 @@
       <c r="N9" s="6"/>
       <c r="O9" s="6"/>
       <c r="P9" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q9" s="8"/>
       <c r="R9" s="8"/>
@@ -1055,7 +1060,7 @@
       <c r="N10" s="6"/>
       <c r="O10" s="6"/>
       <c r="P10" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
@@ -1106,7 +1111,7 @@
       <c r="N11" s="6"/>
       <c r="O11" s="6"/>
       <c r="P11" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q11" s="8"/>
       <c r="R11" s="8"/>
@@ -1157,7 +1162,7 @@
       <c r="N12" s="6"/>
       <c r="O12" s="6"/>
       <c r="P12" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
@@ -1208,7 +1213,7 @@
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
@@ -1259,7 +1264,7 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
@@ -1310,7 +1315,7 @@
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
       <c r="P15" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
@@ -1361,7 +1366,7 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
@@ -1412,7 +1417,7 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q17" s="8"/>
       <c r="R17" s="8"/>
@@ -1463,7 +1468,7 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q18" s="9"/>
       <c r="R18" s="9"/>
@@ -1514,7 +1519,7 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
@@ -1565,7 +1570,7 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q20" s="9"/>
       <c r="R20" s="9"/>
@@ -1616,7 +1621,7 @@
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q21" s="8"/>
       <c r="R21" s="8"/>
@@ -1667,7 +1672,7 @@
       <c r="N22" s="6"/>
       <c r="O22" s="6"/>
       <c r="P22" s="9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="9"/>
       <c r="R22" s="9"/>
@@ -1718,7 +1723,7 @@
       <c r="N23" s="6"/>
       <c r="O23" s="6"/>
       <c r="P23" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q23" s="8"/>
       <c r="R23" s="8"/>
@@ -1769,7 +1774,7 @@
       <c r="N24" s="6"/>
       <c r="O24" s="6"/>
       <c r="P24" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q24" s="10"/>
       <c r="R24" s="10"/>
